--- a/Result/profitability/2618.xlsx
+++ b/Result/profitability/2618.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.105</v>
+        <v>0.98625</v>
       </c>
       <c r="N2" t="n">
-        <v>21.745</v>
+        <v>20.0875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.78</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.45875</v>
+        <v>16.05375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4625</v>
+        <v>0.4137500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.20125</v>
+        <v>13.10625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.63</v>
       </c>
       <c r="M5" t="n">
-        <v>0.12125</v>
+        <v>0.05500000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>11.9275</v>
+        <v>10.53375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.02749999999999998</v>
+        <v>-0.07499999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>9.932500000000001</v>
+        <v>8.86875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22375</v>
+        <v>-0.3124999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8125</v>
+        <v>5.71625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.52</v>
+        <v>-0.6224999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>4.325</v>
+        <v>2.81375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>67770</v>
+      </c>
+      <c r="D75" t="n">
+        <v>58194</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9576</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5719</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-388</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5331</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3848</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.3525</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8200000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5359477124183007</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-12.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4610983981693363</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4274193548387097</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.15</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4410601265822784</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
